--- a/data/trans_orig/ED_INF-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,26</t>
+          <t>6,24; 8,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 7,98</t>
+          <t>6,04; 8,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,68</t>
+          <t>6,9; 8,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,87</t>
+          <t>8,33; 10,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,76</t>
+          <t>6,55; 8,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 7,84</t>
+          <t>5,99; 7,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 8,45</t>
+          <t>6,57; 8,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 10,36</t>
+          <t>8,33; 10,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,15</t>
+          <t>6,68; 8,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 7,66</t>
+          <t>6,35; 7,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,26</t>
+          <t>7,06; 8,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 10,28</t>
+          <t>8,66; 10,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 8,12</t>
+          <t>6,67; 8,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,73</t>
+          <t>6,23; 7,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 8,4</t>
+          <t>6,98; 8,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,81</t>
+          <t>9,03; 13,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 8,89</t>
+          <t>7,51; 8,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,94</t>
+          <t>6,54; 7,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,38</t>
+          <t>7,09; 8,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 10,52</t>
+          <t>8,81; 10,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 8,36</t>
+          <t>7,31; 8,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,67</t>
+          <t>6,54; 7,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,14</t>
+          <t>7,17; 8,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 11,46</t>
+          <t>9,2; 11,57</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,22</t>
+          <t>7,22; 9,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,73</t>
+          <t>6,0; 7,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,54</t>
+          <t>6,63; 8,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 10,23</t>
+          <t>8,5; 10,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 8,62</t>
+          <t>6,78; 8,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 8,65</t>
+          <t>6,8; 8,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,51</t>
+          <t>6,73; 8,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 10,4</t>
+          <t>8,7; 10,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 8,7</t>
+          <t>7,33; 8,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 7,99</t>
+          <t>6,7; 7,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 8,29</t>
+          <t>7,02; 8,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 10,1</t>
+          <t>8,89; 10,11</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,82</t>
+          <t>7,01; 8,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,34</t>
+          <t>6,61; 8,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>6,86; 8,65</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8,76; 10,66</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,91; 8,56</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6,72; 8,43</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>6,85; 8,65</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8,73; 10,54</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6,97; 8,53</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,57; 8,31</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,97; 8,61</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 11,78</t>
+          <t>8,58; 12,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 8,41</t>
+          <t>7,16; 8,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 8,16</t>
+          <t>6,92; 8,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 8,42</t>
+          <t>7,17; 8,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 10,95</t>
+          <t>9,0; 11,03</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,39</t>
+          <t>6,17; 8,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,8</t>
+          <t>6,52; 8,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,31</t>
+          <t>6,16; 8,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,06</t>
+          <t>8,03; 10,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,87</t>
+          <t>6,63; 8,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,9</t>
+          <t>6,51; 8,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,97</t>
+          <t>6,47; 9,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 11,11</t>
+          <t>9,18; 11,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,28</t>
+          <t>6,73; 8,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,45</t>
+          <t>6,89; 8,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,29</t>
+          <t>6,67; 8,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 10,31</t>
+          <t>8,99; 10,38</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 9,09</t>
+          <t>7,08; 9,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 8,84</t>
+          <t>6,76; 8,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,21; 9,19</t>
+          <t>7,22; 9,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 10,32</t>
+          <t>8,34; 10,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 9,21</t>
+          <t>7,35; 9,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,74</t>
+          <t>6,56; 8,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,85</t>
+          <t>6,77; 8,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,13</t>
+          <t>8,16; 10,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,93</t>
+          <t>7,47; 8,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 8,49</t>
+          <t>6,95; 8,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 8,69</t>
+          <t>7,25; 8,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,53; 9,87</t>
+          <t>8,54; 9,95</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 8,36</t>
+          <t>7,08; 8,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,96</t>
+          <t>6,5; 7,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,22</t>
+          <t>6,98; 8,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 9,95</t>
+          <t>8,62; 9,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 8,04</t>
+          <t>6,65; 8,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,52</t>
+          <t>6,2; 7,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,23</t>
+          <t>6,86; 8,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,06; 10,47</t>
+          <t>9,07; 10,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,09; 8,08</t>
+          <t>7,04; 7,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,5</t>
+          <t>6,56; 7,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,02</t>
+          <t>7,09; 8,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 10,08</t>
+          <t>9,12; 10,11</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,25</t>
+          <t>7,08; 8,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,0</t>
+          <t>6,79; 7,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,72</t>
+          <t>6,63; 7,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,86; 10,07</t>
+          <t>8,82; 10,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,02</t>
+          <t>6,83; 7,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,73</t>
+          <t>6,67; 7,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,85</t>
+          <t>6,69; 7,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,91</t>
+          <t>8,72; 9,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,96</t>
+          <t>7,15; 7,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,71</t>
+          <t>6,87; 7,7</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,61</t>
+          <t>6,82; 7,65</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,79</t>
+          <t>8,92; 9,79</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,01</t>
+          <t>7,41; 7,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,57</t>
+          <t>6,99; 7,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,86</t>
+          <t>7,29; 7,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,26; 10,26</t>
+          <t>9,22; 10,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,98</t>
+          <t>7,43; 7,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,55</t>
+          <t>6,97; 7,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,29; 7,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,9</t>
+          <t>9,24; 9,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,88</t>
+          <t>7,49; 7,91</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,47</t>
+          <t>7,05; 7,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,76</t>
+          <t>7,36; 7,77</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,95</t>
+          <t>9,36; 9,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_INF-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,62 +648,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,97</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,51</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,68</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,78</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9,18</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7,45</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6,98</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>7,63</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,97</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,51</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,47</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7,63</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>9,45</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,3</t>
+          <t>6,6; 8,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,0</t>
+          <t>5,99; 7,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 8,69</t>
+          <t>6,54; 8,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,72</t>
+          <t>8,73; 10,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,73</t>
+          <t>6,27; 8,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 7,84</t>
+          <t>5,93; 7,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,41</t>
+          <t>6,89; 8,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,47</t>
+          <t>8,39; 10,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,13</t>
+          <t>6,74; 8,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 7,68</t>
+          <t>6,37; 7,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 8,32</t>
+          <t>7,02; 8,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 10,21</t>
+          <t>8,77; 10,08</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,66</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,82</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,38</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,98</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,69</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,47</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,18</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>9,71</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,15</t>
+          <t>7,45; 8,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,74</t>
+          <t>6,5; 7,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,39</t>
+          <t>7,06; 8,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 13,15</t>
+          <t>9,02; 10,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,9</t>
+          <t>6,66; 8,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,9</t>
+          <t>6,19; 7,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 8,35</t>
+          <t>7,02; 8,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,42</t>
+          <t>8,9; 10,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,34</t>
+          <t>7,32; 8,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,59</t>
+          <t>6,57; 7,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,09</t>
+          <t>7,2; 8,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 11,57</t>
+          <t>9,17; 10,32</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,74</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,65</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,67</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,85</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,62</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,68</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,74</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,65</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>9,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,26</t>
+          <t>6,84; 8,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,72</t>
+          <t>6,85; 8,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,56</t>
+          <t>6,76; 8,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,25</t>
+          <t>8,93; 10,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 8,51</t>
+          <t>7,26; 9,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,67</t>
+          <t>6,03; 7,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,59</t>
+          <t>6,66; 8,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 10,39</t>
+          <t>8,77; 10,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,68</t>
+          <t>7,3; 8,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,97</t>
+          <t>6,6; 7,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,29</t>
+          <t>6,95; 8,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 10,11</t>
+          <t>9,04; 10,17</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,47</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,98</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,71</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,74</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,47</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,8</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>10,0</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 8,77</t>
+          <t>6,89; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,44</t>
+          <t>6,69; 8,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,65</t>
+          <t>6,98; 8,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 10,66</t>
+          <t>8,85; 11,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,56</t>
+          <t>7,05; 8,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,43</t>
+          <t>6,7; 8,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 8,65</t>
+          <t>6,79; 8,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,01</t>
+          <t>9,11; 10,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,39</t>
+          <t>7,15; 8,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,07</t>
+          <t>6,9; 8,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,32</t>
+          <t>7,19; 8,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 11,03</t>
+          <t>9,26; 11,06</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,7</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,41</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,65</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,19</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,02</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,73</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,8</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,79</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,3</t>
+          <t>6,58; 8,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,74</t>
+          <t>6,57; 8,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,26</t>
+          <t>6,49; 9,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,02</t>
+          <t>9,49; 11,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,82</t>
+          <t>6,27; 8,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,78</t>
+          <t>6,44; 8,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,04</t>
+          <t>6,2; 8,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 11,17</t>
+          <t>8,18; 10,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,28</t>
+          <t>6,72; 8,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 8,48</t>
+          <t>6,91; 8,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,27</t>
+          <t>6,72; 8,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 10,38</t>
+          <t>9,07; 10,46</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8,33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,66</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7,82</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8,07</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7,82</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8,19</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,37</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,33</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,24</t>
+          <t>9,67</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,08</t>
+          <t>7,34; 9,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,91</t>
+          <t>6,52; 8,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,29</t>
+          <t>6,85; 8,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 10,33</t>
+          <t>8,7; 10,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 9,33</t>
+          <t>7,06; 9,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,7</t>
+          <t>6,62; 8,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,87</t>
+          <t>7,19; 9,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,09</t>
+          <t>8,71; 10,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,47; 8,86</t>
+          <t>7,54; 8,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,51</t>
+          <t>6,97; 8,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,73</t>
+          <t>7,22; 8,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,54; 9,95</t>
+          <t>9,06; 10,43</t>
         </is>
       </c>
     </row>
@@ -1488,62 +1488,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9,82</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7,72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7,22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7,59</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,33</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,85</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,53</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>9,57</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7,52</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7,03</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7,56</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>9,7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7,52</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>7,03</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,4</t>
+          <t>6,66; 7,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,96</t>
+          <t>6,21; 7,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,27</t>
+          <t>6,87; 8,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 9,93</t>
+          <t>9,24; 10,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 8,03</t>
+          <t>7,08; 8,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 7,53</t>
+          <t>6,63; 7,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,19</t>
+          <t>6,96; 8,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,43</t>
+          <t>8,86; 10,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,96</t>
+          <t>7,08; 8,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,46</t>
+          <t>6,58; 7,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,09; 8,02</t>
+          <t>7,07; 7,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,11</t>
+          <t>9,27; 10,15</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7,4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9,61</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>7,67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>7,37</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>7,19</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,4</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,36</t>
+          <t>9,7</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,25</t>
+          <t>6,84; 8,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,94</t>
+          <t>6,66; 7,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,72</t>
+          <t>6,64; 7,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,82; 10,09</t>
+          <t>9,04; 10,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,93</t>
+          <t>7,12; 8,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,74</t>
+          <t>6,79; 7,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,79</t>
+          <t>6,64; 7,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 9,93</t>
+          <t>9,23; 10,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,99</t>
+          <t>7,12; 7,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,7</t>
+          <t>6,87; 7,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,65</t>
+          <t>6,8; 7,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,92; 9,79</t>
+          <t>9,29; 10,12</t>
         </is>
       </c>
     </row>
@@ -1768,62 +1768,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,69</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7,26</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,56</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9,78</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7,7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>7,27</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7,69</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>7,26</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,71</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,97</t>
+          <t>7,39; 7,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,57</t>
+          <t>6,97; 7,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,3; 7,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,22; 10,25</t>
+          <t>9,48; 10,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,99</t>
+          <t>7,44; 8,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,54</t>
+          <t>6,96; 7,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,83</t>
+          <t>7,27; 7,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,91</t>
+          <t>9,34; 9,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,91</t>
+          <t>7,48; 7,9</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,44</t>
+          <t>7,06; 7,45</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,77</t>
+          <t>7,35; 7,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,96</t>
+          <t>9,52; 9,93</t>
         </is>
       </c>
     </row>
